--- a/data/obx_xlsx/NAVA.OL.xlsx
+++ b/data/obx_xlsx/NAVA.OL.xlsx
@@ -1467,7 +1467,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1551,6 +1551,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -10956,13 +10959,34 @@
       <c r="P61" s="15">
         <v>0.05</v>
       </c>
-      <c r="Q61" s="21"/>
-      <c r="R61" s="21"/>
-      <c r="S61" s="21"/>
-      <c r="T61" s="21"/>
-      <c r="U61" s="21"/>
-      <c r="V61" s="21"/>
-      <c r="W61" s="21"/>
+      <c r="Q61" s="15">
+        <f t="shared" ref="Q61:S61" si="1">Q66+Q67</f>
+        <v>0.07</v>
+      </c>
+      <c r="R61" s="15">
+        <f t="shared" si="1"/>
+        <v>0.03</v>
+      </c>
+      <c r="S61" s="15">
+        <f t="shared" si="1"/>
+        <v>0.19</v>
+      </c>
+      <c r="T61" s="15">
+        <f t="shared" ref="T61:W61" si="2">T66+T67+T76+T77</f>
+        <v>2.94</v>
+      </c>
+      <c r="U61" s="15">
+        <f t="shared" si="2"/>
+        <v>4.91</v>
+      </c>
+      <c r="V61" s="15">
+        <f t="shared" si="2"/>
+        <v>0.26</v>
+      </c>
+      <c r="W61" s="15">
+        <f t="shared" si="2"/>
+        <v>0.34</v>
+      </c>
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="13" t="s">
@@ -11858,9 +11882,15 @@
       <c r="T85" s="15">
         <v>2.0</v>
       </c>
-      <c r="U85" s="21"/>
-      <c r="V85" s="21"/>
-      <c r="W85" s="21"/>
+      <c r="U85" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="V85" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="W85" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="13" t="s">
@@ -17968,7 +17998,7 @@
       <c r="A68" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="B68" s="28">
+      <c r="B68" s="29">
         <v>-186.65</v>
       </c>
       <c r="C68" s="21"/>
@@ -18030,13 +18060,13 @@
       <c r="A70" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="B70" s="29">
+      <c r="B70" s="30">
         <v>-186.65</v>
       </c>
       <c r="C70" s="26">
         <v>-2.78</v>
       </c>
-      <c r="D70" s="29">
+      <c r="D70" s="30">
         <v>-104.58</v>
       </c>
       <c r="E70" s="26">
@@ -20640,2269 +20670,2269 @@
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="31" t="s">
         <v>390</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="33" t="s">
         <v>390</v>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="34">
         <v>520.23</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="34">
         <v>751.44</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="34">
         <v>594.58</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="34">
         <v>549.78</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="34">
         <v>275.28</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="34">
         <v>233.65</v>
       </c>
-      <c r="H20" s="33">
+      <c r="H20" s="34">
         <v>140.52</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="35">
         <v>83.54</v>
       </c>
-      <c r="J20" s="33">
+      <c r="J20" s="34">
         <v>158.78</v>
       </c>
-      <c r="K20" s="33">
+      <c r="K20" s="34">
         <v>114.02</v>
       </c>
-      <c r="L20" s="33">
+      <c r="L20" s="34">
         <v>112.66</v>
       </c>
-      <c r="M20" s="33">
+      <c r="M20" s="34">
         <v>106.09</v>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="35">
         <v>79.99</v>
       </c>
-      <c r="O20" s="34">
+      <c r="O20" s="35">
         <v>74.41</v>
       </c>
-      <c r="P20" s="34">
+      <c r="P20" s="35">
         <v>31.78</v>
       </c>
-      <c r="Q20" s="34">
+      <c r="Q20" s="35">
         <v>16.2</v>
       </c>
-      <c r="R20" s="34">
+      <c r="R20" s="35">
         <v>35.12</v>
       </c>
-      <c r="S20" s="33">
+      <c r="S20" s="34">
         <v>235.23</v>
       </c>
-      <c r="T20" s="33">
+      <c r="T20" s="34">
         <v>118.1</v>
       </c>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="36"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="33" t="s">
         <v>391</v>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="34">
         <v>538.26</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>480.95</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <v>358.76</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <v>256.55</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <v>178.35</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <v>146.1</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="34">
         <v>121.9</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="34">
         <v>115.02</v>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="34">
         <v>114.31</v>
       </c>
-      <c r="K21" s="34">
+      <c r="K21" s="35">
         <v>97.43</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="35">
         <v>80.99</v>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="35">
         <v>61.69</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="35">
         <v>47.5</v>
       </c>
-      <c r="O21" s="34">
+      <c r="O21" s="35">
         <v>78.55</v>
       </c>
-      <c r="P21" s="34">
+      <c r="P21" s="35">
         <v>87.29</v>
       </c>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="36"/>
+      <c r="W21" s="36"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="31" t="s">
         <v>392</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="33" t="s">
         <v>392</v>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="34">
         <v>453.93</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="34">
         <v>636.85</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="34">
         <v>601.25</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="34">
         <v>555.75</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="34">
         <v>292.08</v>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="34">
         <v>219.55</v>
       </c>
-      <c r="H23" s="33">
+      <c r="H23" s="34">
         <v>118.99</v>
       </c>
-      <c r="I23" s="33">
+      <c r="I23" s="34">
         <v>101.58</v>
       </c>
-      <c r="J23" s="33">
+      <c r="J23" s="34">
         <v>126.73</v>
       </c>
-      <c r="K23" s="34">
+      <c r="K23" s="35">
         <v>90.43</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="35">
         <v>91.46</v>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="35">
         <v>95.85</v>
       </c>
-      <c r="N23" s="34">
+      <c r="N23" s="35">
         <v>83.62</v>
       </c>
-      <c r="O23" s="34">
+      <c r="O23" s="35">
         <v>73.8</v>
       </c>
-      <c r="P23" s="34">
+      <c r="P23" s="35">
         <v>44.35</v>
       </c>
-      <c r="Q23" s="34">
+      <c r="Q23" s="35">
         <v>50.25</v>
       </c>
-      <c r="R23" s="34">
+      <c r="R23" s="35">
         <v>33.41</v>
       </c>
-      <c r="S23" s="33">
+      <c r="S23" s="34">
         <v>251.59</v>
       </c>
-      <c r="T23" s="33">
+      <c r="T23" s="34">
         <v>142.52</v>
       </c>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="36"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="33" t="s">
         <v>393</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="34">
         <v>507.97</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="34">
         <v>461.1</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="34">
         <v>357.52</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="34">
         <v>257.59</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="34">
         <v>171.78</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="34">
         <v>131.45</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="34">
         <v>105.84</v>
       </c>
-      <c r="I24" s="33">
+      <c r="I24" s="34">
         <v>101.21</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="35">
         <v>97.62</v>
       </c>
-      <c r="K24" s="34">
+      <c r="K24" s="35">
         <v>87.03</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="35">
         <v>77.81</v>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="35">
         <v>69.57</v>
       </c>
-      <c r="N24" s="34">
+      <c r="N24" s="35">
         <v>57.09</v>
       </c>
-      <c r="O24" s="34">
+      <c r="O24" s="35">
         <v>90.68</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="34">
         <v>104.42</v>
       </c>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="33" t="s">
         <v>395</v>
       </c>
-      <c r="B26" s="34">
+      <c r="B26" s="35">
         <v>25.27</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="35">
         <v>36.09</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="35">
         <v>34.32</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="35">
         <v>33.43</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="35">
         <v>18.78</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="35">
         <v>18.16</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="35">
         <v>10.75</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="35">
         <v>9.18</v>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="35">
         <v>11.45</v>
       </c>
-      <c r="K26" s="34">
+      <c r="K26" s="35">
         <v>9.4</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="35">
         <v>10.49</v>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="35">
         <v>11.06</v>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="35">
         <v>9.79</v>
       </c>
-      <c r="O26" s="34">
+      <c r="O26" s="35">
         <v>9.61</v>
       </c>
-      <c r="P26" s="34">
+      <c r="P26" s="35">
         <v>5.78</v>
       </c>
-      <c r="Q26" s="34">
+      <c r="Q26" s="35">
         <v>6.55</v>
       </c>
-      <c r="R26" s="34">
+      <c r="R26" s="35">
         <v>4.35</v>
       </c>
-      <c r="S26" s="34">
+      <c r="S26" s="35">
         <v>32.78</v>
       </c>
-      <c r="T26" s="34">
+      <c r="T26" s="35">
         <v>23.42</v>
       </c>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="33" t="s">
         <v>396</v>
       </c>
-      <c r="B27" s="34">
+      <c r="B27" s="35">
         <v>29.58</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>28.16</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="35">
         <v>23.09</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <v>18.06</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="35">
         <v>13.66</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="35">
         <v>11.79</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="35">
         <v>10.25</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="35">
         <v>10.31</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="35">
         <v>10.44</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="35">
         <v>10.07</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="35">
         <v>9.35</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="35">
         <v>8.56</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <v>7.22</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="35">
         <v>11.81</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="35">
         <v>14.58</v>
       </c>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="31" t="s">
         <v>397</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="33" t="s">
         <v>398</v>
       </c>
-      <c r="B29" s="36">
+      <c r="B29" s="37">
         <v>6.41</v>
       </c>
-      <c r="C29" s="37">
+      <c r="C29" s="38">
         <v>-1.05</v>
       </c>
-      <c r="D29" s="36">
+      <c r="D29" s="37">
         <v>2.08</v>
       </c>
-      <c r="E29" s="37">
+      <c r="E29" s="38">
         <v>-0.63</v>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="38">
         <v>-3.62</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="37">
         <v>5.28</v>
       </c>
-      <c r="H29" s="37">
+      <c r="H29" s="38">
         <v>-32.09</v>
       </c>
-      <c r="I29" s="36">
+      <c r="I29" s="37">
         <v>51.2</v>
       </c>
-      <c r="J29" s="37">
+      <c r="J29" s="38">
         <v>-13.5</v>
       </c>
-      <c r="K29" s="36">
+      <c r="K29" s="37">
         <v>26.01</v>
       </c>
-      <c r="L29" s="37">
+      <c r="L29" s="38">
         <v>-12.74</v>
       </c>
-      <c r="M29" s="37">
+      <c r="M29" s="38">
         <v>-18.68</v>
       </c>
-      <c r="N29" s="37">
+      <c r="N29" s="38">
         <v>-7.95</v>
       </c>
-      <c r="O29" s="37">
+      <c r="O29" s="38">
         <v>-19.97</v>
       </c>
-      <c r="P29" s="37">
+      <c r="P29" s="38">
         <v>-32.24</v>
       </c>
-      <c r="Q29" s="37">
+      <c r="Q29" s="38">
         <v>-3.13</v>
       </c>
-      <c r="R29" s="37">
+      <c r="R29" s="38">
         <v>-30.99</v>
       </c>
-      <c r="S29" s="36">
+      <c r="S29" s="37">
         <v>1.36</v>
       </c>
-      <c r="T29" s="37">
+      <c r="T29" s="38">
         <v>-11.72</v>
       </c>
-      <c r="U29" s="36"/>
-      <c r="V29" s="36"/>
-      <c r="W29" s="36"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="33" t="s">
         <v>399</v>
       </c>
-      <c r="B30" s="36">
+      <c r="B30" s="37">
         <v>0.72</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>0.29</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="38">
         <v>-2.31</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="37">
         <v>1.46</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="38">
         <v>-0.03</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="37">
         <v>5.27</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <v>1.58</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="37">
         <v>4.26</v>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="38">
         <v>-6.29</v>
       </c>
-      <c r="K30" s="37">
+      <c r="K30" s="38">
         <v>-7.26</v>
       </c>
-      <c r="L30" s="37">
+      <c r="L30" s="38">
         <v>-17.04</v>
       </c>
-      <c r="M30" s="37">
+      <c r="M30" s="38">
         <v>-15.97</v>
       </c>
-      <c r="N30" s="37">
+      <c r="N30" s="38">
         <v>-16.95</v>
       </c>
-      <c r="O30" s="37">
+      <c r="O30" s="38">
         <v>-8.28</v>
       </c>
-      <c r="P30" s="37">
+      <c r="P30" s="38">
         <v>-7.84</v>
       </c>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="36"/>
-      <c r="S30" s="36"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="36"/>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="37"/>
+      <c r="S30" s="37"/>
+      <c r="T30" s="37"/>
+      <c r="U30" s="37"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="31"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="32"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="33" t="s">
         <v>401</v>
       </c>
-      <c r="B32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="C32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="D32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="E32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="F32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="M32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="N32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="O32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="P32" s="36">
+      <c r="B32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="D32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="E32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="F32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="J32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="M32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="P32" s="37">
         <v>12.24</v>
       </c>
-      <c r="Q32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="R32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="S32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="T32" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="U32" s="36"/>
-      <c r="V32" s="36"/>
-      <c r="W32" s="36"/>
+      <c r="Q32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="R32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="S32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="T32" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="U32" s="37"/>
+      <c r="V32" s="37"/>
+      <c r="W32" s="37"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="33" t="s">
         <v>402</v>
       </c>
-      <c r="B33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="C33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="D33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="J33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="36">
+      <c r="B33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="D33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="E33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="J33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="37">
         <v>1.51</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="37">
         <v>1.65</v>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="37">
         <v>1.96</v>
       </c>
-      <c r="O33" s="36">
+      <c r="O33" s="37">
         <v>1.2</v>
       </c>
-      <c r="P33" s="36">
+      <c r="P33" s="37">
         <v>0.97</v>
       </c>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="36"/>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="36"/>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="37"/>
+      <c r="S33" s="37"/>
+      <c r="T33" s="37"/>
+      <c r="U33" s="37"/>
+      <c r="V33" s="37"/>
+      <c r="W33" s="37"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="33" t="s">
         <v>403</v>
       </c>
-      <c r="B34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="C34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="D34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="E34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="36">
+      <c r="B34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="D34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="37">
         <v>17.0</v>
       </c>
-      <c r="Q34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="R34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="S34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="T34" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="U34" s="36"/>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
+      <c r="Q34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="R34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="S34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="T34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="U34" s="37"/>
+      <c r="V34" s="37"/>
+      <c r="W34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="33" t="s">
         <v>404</v>
       </c>
-      <c r="B35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="C35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="36">
+      <c r="B35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="37">
         <v>2.1</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="37">
         <v>2.3</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="37">
         <v>2.72</v>
       </c>
-      <c r="O35" s="36">
+      <c r="O35" s="37">
         <v>1.66</v>
       </c>
-      <c r="P35" s="36">
+      <c r="P35" s="37">
         <v>1.35</v>
       </c>
-      <c r="Q35" s="36"/>
-      <c r="R35" s="36"/>
-      <c r="S35" s="36"/>
-      <c r="T35" s="36"/>
-      <c r="U35" s="36"/>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
+      <c r="Q35" s="37"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="37"/>
+      <c r="T35" s="37"/>
+      <c r="U35" s="37"/>
+      <c r="V35" s="37"/>
+      <c r="W35" s="37"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="31" t="s">
         <v>405</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="32"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="33" t="s">
         <v>406</v>
       </c>
-      <c r="B37" s="34">
+      <c r="B37" s="35">
         <v>2.1</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="35">
         <v>3.1</v>
       </c>
-      <c r="D37" s="34">
+      <c r="D37" s="35">
         <v>2.87</v>
       </c>
-      <c r="E37" s="34">
+      <c r="E37" s="35">
         <v>3.67</v>
       </c>
-      <c r="F37" s="34">
+      <c r="F37" s="35">
         <v>2.26</v>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="35">
         <v>2.44</v>
       </c>
-      <c r="H37" s="34">
+      <c r="H37" s="35">
         <v>1.04</v>
       </c>
-      <c r="I37" s="34">
+      <c r="I37" s="35">
         <v>0.91</v>
       </c>
-      <c r="J37" s="34">
+      <c r="J37" s="35">
         <v>1.04</v>
       </c>
-      <c r="K37" s="34">
+      <c r="K37" s="35">
         <v>0.76</v>
       </c>
-      <c r="L37" s="34">
+      <c r="L37" s="35">
         <v>0.86</v>
       </c>
-      <c r="M37" s="34">
+      <c r="M37" s="35">
         <v>0.92</v>
       </c>
-      <c r="N37" s="34">
+      <c r="N37" s="35">
         <v>0.86</v>
       </c>
-      <c r="O37" s="34">
+      <c r="O37" s="35">
         <v>0.79</v>
       </c>
-      <c r="P37" s="34">
+      <c r="P37" s="35">
         <v>0.44</v>
       </c>
-      <c r="Q37" s="34">
+      <c r="Q37" s="35">
         <v>0.45</v>
       </c>
-      <c r="R37" s="34">
+      <c r="R37" s="35">
         <v>0.3</v>
       </c>
-      <c r="S37" s="34">
+      <c r="S37" s="35">
         <v>2.28</v>
       </c>
-      <c r="T37" s="34">
+      <c r="T37" s="35">
         <v>3.1</v>
       </c>
-      <c r="U37" s="35"/>
-      <c r="V37" s="35"/>
-      <c r="W37" s="35"/>
+      <c r="U37" s="36"/>
+      <c r="V37" s="36"/>
+      <c r="W37" s="36"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="33" t="s">
         <v>407</v>
       </c>
-      <c r="B38" s="34">
+      <c r="B38" s="35">
         <v>2.79</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="35">
         <v>2.9</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="35">
         <v>2.45</v>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="35">
         <v>2.0</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="35">
         <v>1.45</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="35">
         <v>1.15</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="35">
         <v>0.92</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="35">
         <v>0.89</v>
       </c>
-      <c r="J38" s="34">
+      <c r="J38" s="35">
         <v>0.88</v>
       </c>
-      <c r="K38" s="34">
+      <c r="K38" s="35">
         <v>0.84</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="35">
         <v>0.77</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="35">
         <v>0.68</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="35">
         <v>0.55</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="35">
         <v>0.86</v>
       </c>
-      <c r="P38" s="34">
+      <c r="P38" s="35">
         <v>1.14</v>
       </c>
-      <c r="Q38" s="35"/>
-      <c r="R38" s="35"/>
-      <c r="S38" s="35"/>
-      <c r="T38" s="35"/>
-      <c r="U38" s="35"/>
-      <c r="V38" s="35"/>
-      <c r="W38" s="35"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="36"/>
+      <c r="V38" s="36"/>
+      <c r="W38" s="36"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="31" t="s">
         <v>408</v>
       </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="33" t="s">
         <v>409</v>
       </c>
-      <c r="B40" s="35"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="34">
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="35">
         <v>7.67</v>
       </c>
-      <c r="E40" s="34">
+      <c r="E40" s="35">
         <v>8.84</v>
       </c>
-      <c r="F40" s="34">
+      <c r="F40" s="35">
         <v>5.28</v>
       </c>
-      <c r="G40" s="34">
+      <c r="G40" s="35">
         <v>14.78</v>
       </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="34">
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="35">
         <v>6.16</v>
       </c>
-      <c r="M40" s="34">
+      <c r="M40" s="35">
         <v>15.21</v>
       </c>
-      <c r="N40" s="34">
+      <c r="N40" s="35">
         <v>5.25</v>
       </c>
-      <c r="O40" s="34">
+      <c r="O40" s="35">
         <v>38.83</v>
       </c>
-      <c r="P40" s="34">
+      <c r="P40" s="35">
         <v>2.77</v>
       </c>
-      <c r="Q40" s="34">
+      <c r="Q40" s="35">
         <v>1.68</v>
       </c>
-      <c r="R40" s="34">
+      <c r="R40" s="35">
         <v>3.43</v>
       </c>
-      <c r="S40" s="33">
+      <c r="S40" s="34">
         <v>264.56</v>
       </c>
-      <c r="T40" s="34">
+      <c r="T40" s="35">
         <v>3.1</v>
       </c>
-      <c r="U40" s="35"/>
-      <c r="V40" s="35"/>
-      <c r="W40" s="35"/>
+      <c r="U40" s="36"/>
+      <c r="V40" s="36"/>
+      <c r="W40" s="36"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="B41" s="34">
+      <c r="B41" s="35">
         <v>20.84</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="35">
         <v>13.71</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="35">
         <v>9.64</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="35">
         <v>16.62</v>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="36">
         <v>85611.43</v>
       </c>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="34">
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="35">
         <v>45.23</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="35">
         <v>7.05</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="35">
         <v>4.85</v>
       </c>
-      <c r="N41" s="34">
+      <c r="N41" s="35">
         <v>3.86</v>
       </c>
-      <c r="O41" s="34">
+      <c r="O41" s="35">
         <v>7.75</v>
       </c>
-      <c r="P41" s="34">
+      <c r="P41" s="35">
         <v>4.89</v>
       </c>
-      <c r="Q41" s="35"/>
-      <c r="R41" s="35"/>
-      <c r="S41" s="35"/>
-      <c r="T41" s="35"/>
-      <c r="U41" s="35"/>
-      <c r="V41" s="35"/>
-      <c r="W41" s="35"/>
+      <c r="Q41" s="36"/>
+      <c r="R41" s="36"/>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+      <c r="U41" s="36"/>
+      <c r="V41" s="36"/>
+      <c r="W41" s="36"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="33" t="s">
         <v>412</v>
       </c>
-      <c r="B43" s="34">
+      <c r="B43" s="35">
         <v>0.85</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="35">
         <v>1.24</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="35">
         <v>1.57</v>
       </c>
-      <c r="E43" s="34">
+      <c r="E43" s="35">
         <v>1.99</v>
       </c>
-      <c r="F43" s="34">
+      <c r="F43" s="35">
         <v>1.32</v>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="35">
         <v>1.15</v>
       </c>
-      <c r="H43" s="34">
+      <c r="H43" s="35">
         <v>0.65</v>
       </c>
-      <c r="I43" s="34">
+      <c r="I43" s="35">
         <v>0.39</v>
       </c>
-      <c r="J43" s="34">
+      <c r="J43" s="35">
         <v>0.44</v>
       </c>
-      <c r="K43" s="34">
+      <c r="K43" s="35">
         <v>0.34</v>
       </c>
-      <c r="L43" s="34">
+      <c r="L43" s="35">
         <v>0.41</v>
       </c>
-      <c r="M43" s="34">
+      <c r="M43" s="35">
         <v>0.63</v>
       </c>
-      <c r="N43" s="34">
+      <c r="N43" s="35">
         <v>0.92</v>
       </c>
-      <c r="O43" s="34">
+      <c r="O43" s="35">
         <v>1.04</v>
       </c>
-      <c r="P43" s="34">
+      <c r="P43" s="35">
         <v>0.8</v>
       </c>
-      <c r="Q43" s="34">
+      <c r="Q43" s="35">
         <v>0.96</v>
       </c>
-      <c r="R43" s="34">
+      <c r="R43" s="35">
         <v>0.72</v>
       </c>
-      <c r="S43" s="34">
+      <c r="S43" s="35">
         <v>18.24</v>
       </c>
-      <c r="T43" s="33">
+      <c r="T43" s="34">
         <v>351.11</v>
       </c>
-      <c r="U43" s="35"/>
-      <c r="V43" s="35"/>
-      <c r="W43" s="35"/>
+      <c r="U43" s="36"/>
+      <c r="V43" s="36"/>
+      <c r="W43" s="36"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="33" t="s">
         <v>413</v>
       </c>
-      <c r="B44" s="34">
+      <c r="B44" s="35">
         <v>1.32</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <v>1.44</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="35">
         <v>1.35</v>
       </c>
-      <c r="E44" s="34">
+      <c r="E44" s="35">
         <v>1.04</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="35">
         <v>0.71</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="35">
         <v>0.54</v>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="35">
         <v>0.43</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="35">
         <v>0.43</v>
       </c>
-      <c r="J44" s="34">
+      <c r="J44" s="35">
         <v>0.48</v>
       </c>
-      <c r="K44" s="34">
+      <c r="K44" s="35">
         <v>0.55</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="35">
         <v>0.67</v>
       </c>
-      <c r="M44" s="34">
+      <c r="M44" s="35">
         <v>0.83</v>
       </c>
-      <c r="N44" s="34">
+      <c r="N44" s="35">
         <v>0.9</v>
       </c>
-      <c r="O44" s="34">
+      <c r="O44" s="35">
         <v>1.9</v>
       </c>
-      <c r="P44" s="34">
+      <c r="P44" s="35">
         <v>3.33</v>
       </c>
-      <c r="Q44" s="35"/>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
-      <c r="U44" s="35"/>
-      <c r="V44" s="35"/>
-      <c r="W44" s="35"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+      <c r="U44" s="36"/>
+      <c r="V44" s="36"/>
+      <c r="W44" s="36"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="31" t="s">
         <v>414</v>
       </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="31"/>
-      <c r="P45" s="31"/>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
-      <c r="W45" s="31"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="33" t="s">
         <v>415</v>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="35">
         <v>15.61</v>
       </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="34">
+      <c r="C46" s="36"/>
+      <c r="D46" s="35">
         <v>48.15</v>
       </c>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="34">
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="35">
         <v>18.96</v>
       </c>
-      <c r="H46" s="35"/>
-      <c r="I46" s="34">
+      <c r="H46" s="36"/>
+      <c r="I46" s="35">
         <v>1.95</v>
       </c>
-      <c r="J46" s="35"/>
-      <c r="K46" s="34">
+      <c r="J46" s="36"/>
+      <c r="K46" s="35">
         <v>3.84</v>
       </c>
-      <c r="L46" s="35"/>
-      <c r="M46" s="35"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="34">
+      <c r="L46" s="36"/>
+      <c r="M46" s="36"/>
+      <c r="N46" s="36"/>
+      <c r="O46" s="36"/>
+      <c r="P46" s="36"/>
+      <c r="Q46" s="36"/>
+      <c r="R46" s="36"/>
+      <c r="S46" s="35">
         <v>73.32</v>
       </c>
-      <c r="T46" s="35"/>
-      <c r="U46" s="35"/>
-      <c r="V46" s="35"/>
-      <c r="W46" s="35"/>
+      <c r="T46" s="36"/>
+      <c r="U46" s="36"/>
+      <c r="V46" s="36"/>
+      <c r="W46" s="36"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="33" t="s">
         <v>416</v>
       </c>
-      <c r="B47" s="33">
+      <c r="B47" s="34">
         <v>139.15</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="34">
         <v>350.26</v>
       </c>
-      <c r="D47" s="35"/>
-      <c r="E47" s="34">
+      <c r="D47" s="36"/>
+      <c r="E47" s="35">
         <v>68.63</v>
       </c>
-      <c r="F47" s="33">
+      <c r="F47" s="34">
         <v>1081.33</v>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="35">
         <v>18.98</v>
       </c>
-      <c r="H47" s="34">
+      <c r="H47" s="35">
         <v>63.23</v>
       </c>
-      <c r="I47" s="34">
+      <c r="I47" s="35">
         <v>23.48</v>
       </c>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="35"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
-      <c r="U47" s="35"/>
-      <c r="V47" s="35"/>
-      <c r="W47" s="35"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="36"/>
+      <c r="P47" s="36"/>
+      <c r="Q47" s="36"/>
+      <c r="R47" s="36"/>
+      <c r="S47" s="36"/>
+      <c r="T47" s="36"/>
+      <c r="U47" s="36"/>
+      <c r="V47" s="36"/>
+      <c r="W47" s="36"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="31" t="s">
         <v>417</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="31"/>
-      <c r="T48" s="31"/>
-      <c r="U48" s="31"/>
-      <c r="V48" s="31"/>
-      <c r="W48" s="31"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="33" t="s">
         <v>418</v>
       </c>
-      <c r="B49" s="34">
+      <c r="B49" s="35">
         <v>48.49</v>
       </c>
-      <c r="C49" s="35"/>
-      <c r="D49" s="34">
+      <c r="C49" s="36"/>
+      <c r="D49" s="35">
         <v>16.39</v>
       </c>
-      <c r="E49" s="34">
+      <c r="E49" s="35">
         <v>75.55</v>
       </c>
-      <c r="F49" s="35"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="34">
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="35">
         <v>19.61</v>
       </c>
-      <c r="I49" s="35"/>
-      <c r="J49" s="34">
+      <c r="I49" s="36"/>
+      <c r="J49" s="35">
         <v>35.15</v>
       </c>
-      <c r="K49" s="34">
+      <c r="K49" s="35">
         <v>48.76</v>
       </c>
-      <c r="L49" s="34">
+      <c r="L49" s="35">
         <v>10.16</v>
       </c>
-      <c r="M49" s="34">
+      <c r="M49" s="35">
         <v>18.35</v>
       </c>
-      <c r="N49" s="34">
+      <c r="N49" s="35">
         <v>27.35</v>
       </c>
-      <c r="O49" s="35"/>
-      <c r="P49" s="35"/>
-      <c r="Q49" s="34">
+      <c r="O49" s="36"/>
+      <c r="P49" s="36"/>
+      <c r="Q49" s="35">
         <v>12.71</v>
       </c>
-      <c r="R49" s="34">
+      <c r="R49" s="35">
         <v>5.99</v>
       </c>
-      <c r="S49" s="34">
+      <c r="S49" s="35">
         <v>45.64</v>
       </c>
-      <c r="T49" s="35"/>
-      <c r="U49" s="35"/>
-      <c r="V49" s="35"/>
-      <c r="W49" s="35"/>
+      <c r="T49" s="36"/>
+      <c r="U49" s="36"/>
+      <c r="V49" s="36"/>
+      <c r="W49" s="36"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="33" t="s">
         <v>419</v>
       </c>
-      <c r="B50" s="34">
+      <c r="B50" s="35">
         <v>70.88</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>280.07</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>100.3</v>
       </c>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="34">
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="35">
         <v>29.18</v>
       </c>
-      <c r="I50" s="34">
+      <c r="I50" s="35">
         <v>28.47</v>
       </c>
-      <c r="J50" s="34">
+      <c r="J50" s="35">
         <v>20.78</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="35">
         <v>23.66</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="35">
         <v>34.7</v>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="35">
         <v>51.57</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="35">
         <v>37.85</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="35">
         <v>44.97</v>
       </c>
-      <c r="P50" s="34">
+      <c r="P50" s="35">
         <v>96.28</v>
       </c>
-      <c r="Q50" s="35"/>
-      <c r="R50" s="35"/>
-      <c r="S50" s="35"/>
-      <c r="T50" s="35"/>
-      <c r="U50" s="35"/>
-      <c r="V50" s="35"/>
-      <c r="W50" s="35"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="36"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36"/>
+      <c r="U50" s="36"/>
+      <c r="V50" s="36"/>
+      <c r="W50" s="36"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
-      <c r="N51" s="31"/>
-      <c r="O51" s="31"/>
-      <c r="P51" s="31"/>
-      <c r="Q51" s="31"/>
-      <c r="R51" s="31"/>
-      <c r="S51" s="31"/>
-      <c r="T51" s="31"/>
-      <c r="U51" s="31"/>
-      <c r="V51" s="31"/>
-      <c r="W51" s="31"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="32"/>
+      <c r="P51" s="32"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="32" t="s">
+      <c r="A52" s="33" t="s">
         <v>421</v>
       </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="34">
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="35">
         <v>20.17</v>
       </c>
-      <c r="E52" s="33">
+      <c r="E52" s="34">
         <v>896.61</v>
       </c>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="34">
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="35">
         <v>31.69</v>
       </c>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="35"/>
-      <c r="L52" s="35"/>
-      <c r="M52" s="35"/>
-      <c r="N52" s="35"/>
-      <c r="O52" s="35"/>
-      <c r="P52" s="35"/>
-      <c r="Q52" s="35"/>
-      <c r="R52" s="35"/>
-      <c r="S52" s="35"/>
-      <c r="T52" s="35"/>
-      <c r="U52" s="35"/>
-      <c r="V52" s="35"/>
-      <c r="W52" s="35"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="36"/>
+      <c r="K52" s="36"/>
+      <c r="L52" s="36"/>
+      <c r="M52" s="36"/>
+      <c r="N52" s="36"/>
+      <c r="O52" s="36"/>
+      <c r="P52" s="36"/>
+      <c r="Q52" s="36"/>
+      <c r="R52" s="36"/>
+      <c r="S52" s="36"/>
+      <c r="T52" s="36"/>
+      <c r="U52" s="36"/>
+      <c r="V52" s="36"/>
+      <c r="W52" s="36"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="31" t="s">
         <v>422</v>
       </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-      <c r="T53" s="31"/>
-      <c r="U53" s="31"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="31"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
+      <c r="U53" s="32"/>
+      <c r="V53" s="32"/>
+      <c r="W53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="32" t="s">
+      <c r="A54" s="33" t="s">
         <v>423</v>
       </c>
-      <c r="B54" s="34">
+      <c r="B54" s="35">
         <v>56.76</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="35">
         <v>22.26</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="35">
         <v>16.22</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <v>896.61</v>
       </c>
-      <c r="F54" s="35"/>
-      <c r="G54" s="34">
+      <c r="F54" s="36"/>
+      <c r="G54" s="35">
         <v>3.0</v>
       </c>
-      <c r="H54" s="34">
+      <c r="H54" s="35">
         <v>31.69</v>
       </c>
-      <c r="I54" s="35"/>
-      <c r="J54" s="35"/>
-      <c r="K54" s="35"/>
-      <c r="L54" s="35"/>
-      <c r="M54" s="35"/>
-      <c r="N54" s="35"/>
-      <c r="O54" s="35"/>
-      <c r="P54" s="35"/>
-      <c r="Q54" s="35"/>
-      <c r="R54" s="35"/>
-      <c r="S54" s="33">
+      <c r="I54" s="36"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="36"/>
+      <c r="S54" s="34">
         <v>230.33</v>
       </c>
-      <c r="T54" s="35"/>
-      <c r="U54" s="35"/>
-      <c r="V54" s="35"/>
-      <c r="W54" s="35"/>
+      <c r="T54" s="36"/>
+      <c r="U54" s="36"/>
+      <c r="V54" s="36"/>
+      <c r="W54" s="36"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="32" t="s">
+      <c r="A55" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="B55" s="34">
+      <c r="B55" s="35">
         <v>2.79</v>
       </c>
-      <c r="C55" s="34">
+      <c r="C55" s="35">
         <v>2.9</v>
       </c>
-      <c r="D55" s="34">
+      <c r="D55" s="35">
         <v>2.45</v>
       </c>
-      <c r="E55" s="34">
+      <c r="E55" s="35">
         <v>2.0</v>
       </c>
-      <c r="F55" s="34">
+      <c r="F55" s="35">
         <v>1.45</v>
       </c>
-      <c r="G55" s="34">
+      <c r="G55" s="35">
         <v>1.15</v>
       </c>
-      <c r="H55" s="34">
+      <c r="H55" s="35">
         <v>0.92</v>
       </c>
-      <c r="I55" s="34">
+      <c r="I55" s="35">
         <v>0.89</v>
       </c>
-      <c r="J55" s="34">
+      <c r="J55" s="35">
         <v>0.88</v>
       </c>
-      <c r="K55" s="34">
+      <c r="K55" s="35">
         <v>0.84</v>
       </c>
-      <c r="L55" s="34">
+      <c r="L55" s="35">
         <v>0.77</v>
       </c>
-      <c r="M55" s="34">
+      <c r="M55" s="35">
         <v>0.68</v>
       </c>
-      <c r="N55" s="34">
+      <c r="N55" s="35">
         <v>0.55</v>
       </c>
-      <c r="O55" s="34">
+      <c r="O55" s="35">
         <v>0.86</v>
       </c>
-      <c r="P55" s="34">
+      <c r="P55" s="35">
         <v>1.14</v>
       </c>
-      <c r="Q55" s="35"/>
-      <c r="R55" s="35"/>
-      <c r="S55" s="35"/>
-      <c r="T55" s="35"/>
-      <c r="U55" s="35"/>
-      <c r="V55" s="35"/>
-      <c r="W55" s="35"/>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="36"/>
+      <c r="S55" s="36"/>
+      <c r="T55" s="36"/>
+      <c r="U55" s="36"/>
+      <c r="V55" s="36"/>
+      <c r="W55" s="36"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="31" t="s">
         <v>425</v>
       </c>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="31"/>
-      <c r="K56" s="31"/>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
-      <c r="N56" s="31"/>
-      <c r="O56" s="31"/>
-      <c r="P56" s="31"/>
-      <c r="Q56" s="31"/>
-      <c r="R56" s="31"/>
-      <c r="S56" s="31"/>
-      <c r="T56" s="31"/>
-      <c r="U56" s="31"/>
-      <c r="V56" s="31"/>
-      <c r="W56" s="31"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="32"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="T56" s="32"/>
+      <c r="U56" s="32"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="32" t="s">
+      <c r="A57" s="33" t="s">
         <v>426</v>
       </c>
-      <c r="B57" s="35"/>
-      <c r="C57" s="35"/>
-      <c r="D57" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E57" s="34">
+      <c r="B57" s="36"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E57" s="35">
         <v>8.68</v>
       </c>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="34">
+      <c r="F57" s="36"/>
+      <c r="G57" s="36"/>
+      <c r="H57" s="35">
         <v>0.26</v>
       </c>
-      <c r="I57" s="35"/>
-      <c r="J57" s="35"/>
-      <c r="K57" s="35"/>
-      <c r="L57" s="35"/>
-      <c r="M57" s="35"/>
-      <c r="N57" s="35"/>
-      <c r="O57" s="35"/>
-      <c r="P57" s="35"/>
-      <c r="Q57" s="35"/>
-      <c r="R57" s="35"/>
-      <c r="S57" s="35"/>
-      <c r="T57" s="35"/>
-      <c r="U57" s="35"/>
-      <c r="V57" s="35"/>
-      <c r="W57" s="35"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="36"/>
+      <c r="K57" s="36"/>
+      <c r="L57" s="36"/>
+      <c r="M57" s="36"/>
+      <c r="N57" s="36"/>
+      <c r="O57" s="36"/>
+      <c r="P57" s="36"/>
+      <c r="Q57" s="36"/>
+      <c r="R57" s="36"/>
+      <c r="S57" s="36"/>
+      <c r="T57" s="36"/>
+      <c r="U57" s="36"/>
+      <c r="V57" s="36"/>
+      <c r="W57" s="36"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>427</v>
       </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31"/>
-      <c r="T58" s="31"/>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
-      <c r="W58" s="31"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="32" t="s">
+      <c r="A59" s="33" t="s">
         <v>428</v>
       </c>
-      <c r="B59" s="34">
+      <c r="B59" s="35">
         <v>0.98</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="35">
         <v>1.47</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="35">
         <v>1.56</v>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="35">
         <v>1.97</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <v>1.31</v>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="35">
         <v>1.24</v>
       </c>
-      <c r="H59" s="34">
+      <c r="H59" s="35">
         <v>0.76</v>
       </c>
-      <c r="I59" s="34">
+      <c r="I59" s="35">
         <v>0.32</v>
       </c>
-      <c r="J59" s="34">
+      <c r="J59" s="35">
         <v>0.58</v>
       </c>
-      <c r="K59" s="34">
+      <c r="K59" s="35">
         <v>0.46</v>
       </c>
-      <c r="L59" s="34">
+      <c r="L59" s="35">
         <v>0.51</v>
       </c>
-      <c r="M59" s="34">
+      <c r="M59" s="35">
         <v>0.7</v>
       </c>
-      <c r="N59" s="34">
+      <c r="N59" s="35">
         <v>0.9</v>
       </c>
-      <c r="O59" s="34">
+      <c r="O59" s="35">
         <v>1.04</v>
       </c>
-      <c r="P59" s="34">
+      <c r="P59" s="35">
         <v>0.58</v>
       </c>
-      <c r="Q59" s="34">
+      <c r="Q59" s="35">
         <v>0.31</v>
       </c>
-      <c r="R59" s="34">
+      <c r="R59" s="35">
         <v>0.76</v>
       </c>
-      <c r="S59" s="34">
+      <c r="S59" s="35">
         <v>20.29</v>
       </c>
-      <c r="T59" s="33">
+      <c r="T59" s="34">
         <v>305.97</v>
       </c>
-      <c r="U59" s="35"/>
-      <c r="V59" s="35"/>
-      <c r="W59" s="35"/>
+      <c r="U59" s="36"/>
+      <c r="V59" s="36"/>
+      <c r="W59" s="36"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="32" t="s">
+      <c r="A60" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="B60" s="34">
+      <c r="B60" s="35">
         <v>1.41</v>
       </c>
-      <c r="C60" s="34">
+      <c r="C60" s="35">
         <v>1.53</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="35">
         <v>1.44</v>
       </c>
-      <c r="E60" s="34">
+      <c r="E60" s="35">
         <v>1.15</v>
       </c>
-      <c r="F60" s="34">
+      <c r="F60" s="35">
         <v>0.8</v>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="35">
         <v>0.63</v>
       </c>
-      <c r="H60" s="34">
+      <c r="H60" s="35">
         <v>0.51</v>
       </c>
-      <c r="I60" s="34">
+      <c r="I60" s="35">
         <v>0.5</v>
       </c>
-      <c r="J60" s="34">
+      <c r="J60" s="35">
         <v>0.58</v>
       </c>
-      <c r="K60" s="34">
+      <c r="K60" s="35">
         <v>0.62</v>
       </c>
-      <c r="L60" s="34">
+      <c r="L60" s="35">
         <v>0.69</v>
       </c>
-      <c r="M60" s="34">
+      <c r="M60" s="35">
         <v>0.74</v>
       </c>
-      <c r="N60" s="34">
+      <c r="N60" s="35">
         <v>0.76</v>
       </c>
-      <c r="O60" s="34">
+      <c r="O60" s="35">
         <v>1.66</v>
       </c>
-      <c r="P60" s="34">
+      <c r="P60" s="35">
         <v>2.63</v>
       </c>
-      <c r="Q60" s="35"/>
-      <c r="R60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="T60" s="35"/>
-      <c r="U60" s="35"/>
-      <c r="V60" s="35"/>
-      <c r="W60" s="35"/>
+      <c r="Q60" s="36"/>
+      <c r="R60" s="36"/>
+      <c r="S60" s="36"/>
+      <c r="T60" s="36"/>
+      <c r="U60" s="36"/>
+      <c r="V60" s="36"/>
+      <c r="W60" s="36"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="30" t="s">
+      <c r="A61" s="31" t="s">
         <v>430</v>
       </c>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="31"/>
-      <c r="O61" s="31"/>
-      <c r="P61" s="31"/>
-      <c r="Q61" s="31"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="31"/>
-      <c r="T61" s="31"/>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
-      <c r="W61" s="31"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="32" t="s">
+      <c r="A62" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="B62" s="34">
+      <c r="B62" s="35">
         <v>11.18</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="35">
         <v>14.57</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="35">
         <v>11.5</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <v>30.26</v>
       </c>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="34">
+      <c r="F62" s="36"/>
+      <c r="G62" s="36"/>
+      <c r="H62" s="35">
         <v>16.47</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="35">
         <v>11.92</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="35">
         <v>19.77</v>
       </c>
-      <c r="K62" s="34">
+      <c r="K62" s="35">
         <v>12.91</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="35">
         <v>7.16</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="35">
         <v>12.27</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="35">
         <v>39.89</v>
       </c>
-      <c r="O62" s="35"/>
-      <c r="P62" s="35"/>
-      <c r="Q62" s="35"/>
-      <c r="R62" s="34">
+      <c r="O62" s="36"/>
+      <c r="P62" s="36"/>
+      <c r="Q62" s="36"/>
+      <c r="R62" s="35">
         <v>4.88</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="34">
         <v>164.38</v>
       </c>
-      <c r="T62" s="35"/>
-      <c r="U62" s="35"/>
-      <c r="V62" s="35"/>
-      <c r="W62" s="35"/>
+      <c r="T62" s="36"/>
+      <c r="U62" s="36"/>
+      <c r="V62" s="36"/>
+      <c r="W62" s="36"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="32" t="s">
+      <c r="A63" s="33" t="s">
         <v>432</v>
       </c>
-      <c r="B63" s="34">
+      <c r="B63" s="35">
         <v>16.14</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="35">
         <v>21.15</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="35">
         <v>25.39</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="35">
         <v>49.36</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="35">
         <v>56.28</v>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="35">
         <v>28.16</v>
       </c>
-      <c r="H63" s="34">
+      <c r="H63" s="35">
         <v>12.67</v>
       </c>
-      <c r="I63" s="34">
+      <c r="I63" s="35">
         <v>11.92</v>
       </c>
-      <c r="J63" s="34">
+      <c r="J63" s="35">
         <v>13.22</v>
       </c>
-      <c r="K63" s="34">
+      <c r="K63" s="35">
         <v>14.96</v>
       </c>
-      <c r="L63" s="34">
+      <c r="L63" s="35">
         <v>23.48</v>
       </c>
-      <c r="M63" s="35"/>
-      <c r="N63" s="35"/>
-      <c r="O63" s="35"/>
-      <c r="P63" s="35"/>
-      <c r="Q63" s="35"/>
-      <c r="R63" s="35"/>
-      <c r="S63" s="35"/>
-      <c r="T63" s="35"/>
-      <c r="U63" s="35"/>
-      <c r="V63" s="35"/>
-      <c r="W63" s="35"/>
+      <c r="M63" s="36"/>
+      <c r="N63" s="36"/>
+      <c r="O63" s="36"/>
+      <c r="P63" s="36"/>
+      <c r="Q63" s="36"/>
+      <c r="R63" s="36"/>
+      <c r="S63" s="36"/>
+      <c r="T63" s="36"/>
+      <c r="U63" s="36"/>
+      <c r="V63" s="36"/>
+      <c r="W63" s="36"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="31" t="s">
         <v>433</v>
       </c>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="31"/>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="31"/>
-      <c r="Q64" s="31"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
-      <c r="T64" s="31"/>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
-      <c r="W64" s="31"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="32"/>
+      <c r="O64" s="32"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="32"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
+      <c r="W64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="32" t="s">
+      <c r="A65" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="B65" s="34">
+      <c r="B65" s="35">
         <v>16.2</v>
       </c>
-      <c r="C65" s="35"/>
-      <c r="D65" s="34">
+      <c r="C65" s="36"/>
+      <c r="D65" s="35">
         <v>40.34</v>
       </c>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="34">
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="35">
         <v>19.24</v>
       </c>
-      <c r="H65" s="35"/>
-      <c r="I65" s="34">
+      <c r="H65" s="36"/>
+      <c r="I65" s="35">
         <v>1.41</v>
       </c>
-      <c r="J65" s="35"/>
-      <c r="K65" s="34">
+      <c r="J65" s="36"/>
+      <c r="K65" s="35">
         <v>5.04</v>
       </c>
-      <c r="L65" s="35"/>
-      <c r="M65" s="35"/>
-      <c r="N65" s="35"/>
-      <c r="O65" s="35"/>
-      <c r="P65" s="35"/>
-      <c r="Q65" s="35"/>
-      <c r="R65" s="35"/>
-      <c r="S65" s="34">
+      <c r="L65" s="36"/>
+      <c r="M65" s="36"/>
+      <c r="N65" s="36"/>
+      <c r="O65" s="36"/>
+      <c r="P65" s="36"/>
+      <c r="Q65" s="36"/>
+      <c r="R65" s="36"/>
+      <c r="S65" s="35">
         <v>35.09</v>
       </c>
-      <c r="T65" s="35"/>
-      <c r="U65" s="35"/>
-      <c r="V65" s="35"/>
-      <c r="W65" s="35"/>
+      <c r="T65" s="36"/>
+      <c r="U65" s="36"/>
+      <c r="V65" s="36"/>
+      <c r="W65" s="36"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="32" t="s">
+      <c r="A66" s="33" t="s">
         <v>435</v>
       </c>
-      <c r="B66" s="34">
+      <c r="B66" s="35">
         <v>77.69</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="34">
         <v>163.96</v>
       </c>
-      <c r="D66" s="35"/>
-      <c r="E66" s="34">
+      <c r="D66" s="36"/>
+      <c r="E66" s="35">
         <v>50.38</v>
       </c>
-      <c r="F66" s="34">
+      <c r="F66" s="35">
         <v>64.99</v>
       </c>
-      <c r="G66" s="34">
+      <c r="G66" s="35">
         <v>17.66</v>
       </c>
-      <c r="H66" s="34">
+      <c r="H66" s="35">
         <v>33.0</v>
       </c>
-      <c r="I66" s="34">
+      <c r="I66" s="35">
         <v>14.1</v>
       </c>
-      <c r="J66" s="35"/>
-      <c r="K66" s="35"/>
-      <c r="L66" s="35"/>
-      <c r="M66" s="35"/>
-      <c r="N66" s="35"/>
-      <c r="O66" s="35"/>
-      <c r="P66" s="35"/>
-      <c r="Q66" s="35"/>
-      <c r="R66" s="35"/>
-      <c r="S66" s="35"/>
-      <c r="T66" s="35"/>
-      <c r="U66" s="35"/>
-      <c r="V66" s="35"/>
-      <c r="W66" s="35"/>
+      <c r="J66" s="36"/>
+      <c r="K66" s="36"/>
+      <c r="L66" s="36"/>
+      <c r="M66" s="36"/>
+      <c r="N66" s="36"/>
+      <c r="O66" s="36"/>
+      <c r="P66" s="36"/>
+      <c r="Q66" s="36"/>
+      <c r="R66" s="36"/>
+      <c r="S66" s="36"/>
+      <c r="T66" s="36"/>
+      <c r="U66" s="36"/>
+      <c r="V66" s="36"/>
+      <c r="W66" s="36"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="31" t="s">
         <v>436</v>
       </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-      <c r="P67" s="31"/>
-      <c r="Q67" s="31"/>
-      <c r="R67" s="31"/>
-      <c r="S67" s="31"/>
-      <c r="T67" s="31"/>
-      <c r="U67" s="31"/>
-      <c r="V67" s="31"/>
-      <c r="W67" s="31"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
+      <c r="N67" s="32"/>
+      <c r="O67" s="32"/>
+      <c r="P67" s="32"/>
+      <c r="Q67" s="32"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="32"/>
+      <c r="T67" s="32"/>
+      <c r="U67" s="32"/>
+      <c r="V67" s="32"/>
+      <c r="W67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="32" t="s">
+      <c r="A68" s="33" t="s">
         <v>437</v>
       </c>
-      <c r="B68" s="34">
+      <c r="B68" s="35">
         <v>18.07</v>
       </c>
-      <c r="C68" s="35"/>
-      <c r="D68" s="34">
+      <c r="C68" s="36"/>
+      <c r="D68" s="35">
         <v>47.61</v>
       </c>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="34">
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="35">
         <v>20.45</v>
       </c>
-      <c r="H68" s="35"/>
-      <c r="I68" s="34">
+      <c r="H68" s="36"/>
+      <c r="I68" s="35">
         <v>1.61</v>
       </c>
-      <c r="J68" s="35"/>
-      <c r="K68" s="34">
+      <c r="J68" s="36"/>
+      <c r="K68" s="35">
         <v>5.22</v>
       </c>
-      <c r="L68" s="35"/>
-      <c r="M68" s="35"/>
-      <c r="N68" s="35"/>
-      <c r="O68" s="35"/>
-      <c r="P68" s="35"/>
-      <c r="Q68" s="35"/>
-      <c r="R68" s="35"/>
-      <c r="S68" s="34">
+      <c r="L68" s="36"/>
+      <c r="M68" s="36"/>
+      <c r="N68" s="36"/>
+      <c r="O68" s="36"/>
+      <c r="P68" s="36"/>
+      <c r="Q68" s="36"/>
+      <c r="R68" s="36"/>
+      <c r="S68" s="35">
         <v>81.56</v>
       </c>
-      <c r="T68" s="35"/>
-      <c r="U68" s="35"/>
-      <c r="V68" s="35"/>
-      <c r="W68" s="35"/>
+      <c r="T68" s="36"/>
+      <c r="U68" s="36"/>
+      <c r="V68" s="36"/>
+      <c r="W68" s="36"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="32" t="s">
+      <c r="A69" s="33" t="s">
         <v>438</v>
       </c>
-      <c r="B69" s="33">
+      <c r="B69" s="34">
         <v>127.27</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>637.01</v>
       </c>
-      <c r="D69" s="35"/>
-      <c r="E69" s="33">
+      <c r="D69" s="36"/>
+      <c r="E69" s="34">
         <v>109.23</v>
       </c>
-      <c r="F69" s="35"/>
-      <c r="G69" s="34">
+      <c r="F69" s="36"/>
+      <c r="G69" s="35">
         <v>23.63</v>
       </c>
-      <c r="H69" s="34">
+      <c r="H69" s="35">
         <v>77.65</v>
       </c>
-      <c r="I69" s="34">
+      <c r="I69" s="35">
         <v>20.44</v>
       </c>
-      <c r="J69" s="35"/>
-      <c r="K69" s="35"/>
-      <c r="L69" s="35"/>
-      <c r="M69" s="35"/>
-      <c r="N69" s="35"/>
-      <c r="O69" s="35"/>
-      <c r="P69" s="35"/>
-      <c r="Q69" s="35"/>
-      <c r="R69" s="35"/>
-      <c r="S69" s="35"/>
-      <c r="T69" s="35"/>
-      <c r="U69" s="35"/>
-      <c r="V69" s="35"/>
-      <c r="W69" s="35"/>
+      <c r="J69" s="36"/>
+      <c r="K69" s="36"/>
+      <c r="L69" s="36"/>
+      <c r="M69" s="36"/>
+      <c r="N69" s="36"/>
+      <c r="O69" s="36"/>
+      <c r="P69" s="36"/>
+      <c r="Q69" s="36"/>
+      <c r="R69" s="36"/>
+      <c r="S69" s="36"/>
+      <c r="T69" s="36"/>
+      <c r="U69" s="36"/>
+      <c r="V69" s="36"/>
+      <c r="W69" s="36"/>
     </row>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1"/>
